--- a/results/Int Task Remove ACC 1.0/Linea_fi_all.xlsx
+++ b/results/Int Task Remove ACC 1.0/Linea_fi_all.xlsx
@@ -1046,7 +1046,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.0032416502946954638 +/- 0.001476748170763554</t>
+          <t>0.0031925343811394667 +/- 0.0014445423546024345</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
@@ -2246,74 +2246,74 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>-0.0007328072153325538 +/- 0.000566509336027115</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>5.6369785794851966e-05 +/- 0.0004682426078307769</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>-0.010766629086809443 +/- 0.0020856820744081205</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>-0.010766629086809443 +/- 0.0020856820744081205</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>-0.030496054114994342 +/- 0.003081834708644118</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0.039909808342728316 +/- 0.002605235627574149</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0.02057497181510711 +/- 0.0014536411452342115</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0.00045095828635852706 +/- 0.003509443611335599</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0.0002818489289741044 +/- 0.000917633629994351</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>0.009244644870349516 +/- 0.0012654985524601931</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0.4440811724915446 +/- 0.005635851071003375</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>-0.0003945885005636751 +/- 0.0009779792318431314</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>0.2820744081172492 +/- 0.0064478756337446735</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
           <t>-0.0007891770011273725 +/- 0.00057486127548961</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>-5.6369785794785356e-05 +/- 0.000531791495606348</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>-0.010766629086809443 +/- 0.0020856820744081205</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>-0.010766629086809443 +/- 0.0020856820744081205</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>-0.030496054114994342 +/- 0.003081834708644118</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0.039909808342728316 +/- 0.002605235627574149</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0.02057497181510711 +/- 0.0014536411452342115</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0.00045095828635852706 +/- 0.003509443611335599</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0.0002818489289741044 +/- 0.000917633629994351</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>0.009244644870349516 +/- 0.0012654985524601931</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0.4440811724915446 +/- 0.005635851071003375</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>-0.0003945885005636751 +/- 0.0009779792318431314</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>0.2820744081172492 +/- 0.0064478756337446735</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>-0.0007891770011273725 +/- 0.00057486127548961</t>
-        </is>
-      </c>
       <c r="W5" t="inlineStr">
         <is>
           <t>-0.00022547914317923025 +/- 0.0008051215815718971</t>
@@ -2571,7 +2571,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>-0.004847801578353983 +/- 0.0010754669689029951</t>
+          <t>-0.004904171364148791 +/- 0.001040934910519711</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2641,7 +2641,7 @@
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>0.02914317925591885 +/- 0.002596071914243377</t>
+          <t>0.02919954904171367 +/- 0.0025559828745782506</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>-0.0068698060941828395 +/- 0.0018901631145963262</t>
+          <t>-0.006925207756232709 +/- 0.0019071373382890187</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>0.0001108033240997286 +/- 0.0006460888526144324</t>
+          <t>5.540166204986985e-05 +/- 0.0006292419219723266</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.000181818181818183 +/- 0.007651980183888264</t>
+          <t>-0.000242424242424244 +/- 0.007652700178261607</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>-0.013878787878787857 +/- 0.0023542938908551704</t>
+          <t>-0.013818181818181795 +/- 0.0023441308613107686</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -4471,72 +4471,72 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>-0.002617801047120505 +/- 0.0008726003490401314</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>-0.01983711460151256 +/- 0.00342630699770267</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0.0369400814426992 +/- 0.0036906857302063706</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>0.0369400814426992 +/- 0.0036906857302063706</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>0.01803374054682949 +/- 0.0024543366038078866</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0.16329261198371142 +/- 0.007874059834984187</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>-0.029493891797556772 +/- 0.0026281226289881117</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0.061489237929028454 +/- 0.0034518914948567297</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>-0.001977894124491042 +/- 0.002068224413569679</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>0.03571844095404301 +/- 0.004023645483604564</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>0.45636998254799294 +/- 0.00861378295227507</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>-0.012041884816753978 +/- 0.0029554126342945033</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>0.24549156486329257 +/- 0.008726003490401377</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
           <t>-0.0025596276905178296 +/- 0.0009452051663334359</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>-0.01983711460151256 +/- 0.00342630699770267</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0.0369400814426992 +/- 0.0036906857302063706</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>0.0369400814426992 +/- 0.0036906857302063706</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>0.01803374054682949 +/- 0.0024543366038078866</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0.16329261198371142 +/- 0.007874059834984187</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>-0.029493891797556772 +/- 0.0026281226289881117</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0.061489237929028454 +/- 0.0034518914948567297</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>-0.001977894124491042 +/- 0.002068224413569679</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>0.03571844095404301 +/- 0.004023645483604564</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>0.45636998254799294 +/- 0.00861378295227507</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>-0.012041884816753978 +/- 0.0029554126342945033</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>0.24549156486329257 +/- 0.008726003490401377</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>-0.002617801047120505 +/- 0.0008726003490401314</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -4981,7 +4981,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>-0.0002139037433155022 +/- 0.0005954828195539919</t>
+          <t>-0.00016042780748662944 +/- 0.0005882352941176278</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
